--- a/data/corpora/test.xlsx
+++ b/data/corpora/test.xlsx
@@ -1,21 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Student\202507sci\github项目\BERT-OCEn\Fine-tuning-CVDD\data\corpora\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F348CD9F-848B-495F-9A52-0EF7FE3B6C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="225" windowWidth="22230" windowHeight="13980" xr2:uid="{09A259AA-1230-42F1-BBBB-FBDF57CAB412}"/>
+    <workbookView windowWidth="28800" windowHeight="11740"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -25,10 +32,10 @@
     <t>index</t>
   </si>
   <si>
-    <t>用途</t>
-  </si>
-  <si>
-    <t>类别</t>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Category</t>
   </si>
   <si>
     <t>食堂外包服务费</t>
@@ -37,207 +44,207 @@
     <t>空</t>
   </si>
   <si>
+    <t>宜城[地点]所报快艇加油费（[城市]市[地点]加油点）</t>
+  </si>
+  <si>
+    <t>督察领维权抚慰激励金（[姓名1]）</t>
+  </si>
+  <si>
+    <t>情指中心报新警初任培训[数字]人（[姓名2]）</t>
+  </si>
+  <si>
     <t>会议培训</t>
   </si>
   <si>
+    <t>[日期]-[数字]巡特警车辆维修费（[城市]经济技术开发区[单位1]）</t>
+  </si>
+  <si>
     <t>公务用车</t>
   </si>
   <si>
+    <t>[年份]年[月份]月社保单位部分</t>
+  </si>
+  <si>
     <t>人员薪酬</t>
   </si>
   <si>
+    <t>[地点]楼会议室光缆布放（[单位2]）</t>
+  </si>
+  <si>
+    <t>[地点]水上所买健身器材一批[数字]-[数字]（[单位3]）</t>
+  </si>
+  <si>
+    <t>[日期]-[日期]保安服务费（[单位4]）</t>
+  </si>
+  <si>
     <t>物业管理</t>
   </si>
   <si>
+    <t>市局空调维修费（[单位5]）</t>
+  </si>
+  <si>
     <t>玻璃擦、挂钩、胶水等</t>
   </si>
   <si>
+    <t>退休人员报学费（[姓名3]）</t>
+  </si>
+  <si>
+    <t>市局电脑设备维修配件（[单位6]）</t>
+  </si>
+  <si>
+    <t>通信保障买[品牌]高清会议系统一套[数字]-[数字]（[单位7]）</t>
+  </si>
+  <si>
+    <t>[地点]警务站报[年份]年新警入警培训（[姓名4]）</t>
+  </si>
+  <si>
+    <t>[地点]警务站报基层政工干部培训（[姓名5]）</t>
+  </si>
+  <si>
+    <t>[地点]警务站报模拟警情处置培训（[姓名6]）</t>
+  </si>
+  <si>
+    <t>[地点]水上所报厨房线路安装、管道疏通费（[姓名7]）</t>
+  </si>
+  <si>
+    <t>市局[月份]月各部门车维修费（[单位8]）</t>
+  </si>
+  <si>
+    <t>[城市]政工干部培训班费用（[姓名8]）</t>
+  </si>
+  <si>
+    <t>[年份]年[月份]月社保个人部分</t>
+  </si>
+  <si>
+    <t>[单位9]中队报垃圾清运费（[姓名9]）</t>
+  </si>
+  <si>
+    <t>退休支部报印刷品（[单位10]）</t>
+  </si>
+  <si>
     <t>设备/服务采购</t>
   </si>
   <si>
+    <t>[月份]月公办公积金个人</t>
+  </si>
+  <si>
+    <t>[月份]月养老金</t>
+  </si>
+  <si>
+    <t>人口报基础所长班培训费（[姓名10]）</t>
+  </si>
+  <si>
+    <t>（[单位11]）[月份]月外聘人员工资</t>
+  </si>
+  <si>
+    <t>单位教职工[数字]月份工资</t>
+  </si>
+  <si>
+    <t>（[单位12]）外聘人员社会保障代扣专户拨款</t>
+  </si>
+  <si>
+    <t>[月份]月公办养老金单位</t>
+  </si>
+  <si>
+    <t>[单位13]在编人员公积金单位</t>
+  </si>
+  <si>
+    <t>支付非编教职工[数字]月社保</t>
+  </si>
+  <si>
+    <t>人口报基础所长班培训费（[姓名11]）</t>
+  </si>
+  <si>
+    <t>[姓名12]报会议服务</t>
+  </si>
+  <si>
+    <t>[单位14]培训费</t>
+  </si>
+  <si>
+    <t>下水管道疏通及维修费（[单位15]）</t>
+  </si>
+  <si>
+    <t>[月份]月物业服务费</t>
+  </si>
+  <si>
     <t>执法大队燃气管道安装费</t>
   </si>
   <si>
+    <t>[单位16]垃圾处理费</t>
+  </si>
+  <si>
     <t>公务用车保养</t>
   </si>
   <si>
+    <t>[姓名13]报公务接待</t>
+  </si>
+  <si>
     <t>公务接待</t>
   </si>
   <si>
+    <t>[姓名14]报洗车费</t>
+  </si>
+  <si>
     <t>教师外出开会培训</t>
   </si>
   <si>
+    <t>[年份]年第[数字]季度保安费</t>
+  </si>
+  <si>
     <t>印刷品资料试卷</t>
   </si>
   <si>
+    <t>[姓名15]报租车费</t>
+  </si>
+  <si>
     <t>男宿舍水泵维修</t>
   </si>
   <si>
     <t>城镇垃圾处理费</t>
   </si>
   <si>
+    <t>[数字]季度公车运维</t>
+  </si>
+  <si>
+    <t>[姓名16]报洗车费</t>
+  </si>
+  <si>
+    <t>[月份]月公车运维</t>
+  </si>
+  <si>
     <t>公车修理费</t>
   </si>
   <si>
+    <t>[日期]-[日期]月公车运维</t>
+  </si>
+  <si>
+    <t>[单位17]文印费</t>
+  </si>
+  <si>
+    <t>办公室：[地点]调研公务接待费用（[单位18]）</t>
+  </si>
+  <si>
+    <t>（[单位19]）文印室耗材费</t>
+  </si>
+  <si>
+    <t>禁毒买印刷品（[单位20]）</t>
+  </si>
+  <si>
     <t>一体机纸</t>
   </si>
   <si>
+    <t>[数字]购铲刀、链条</t>
+  </si>
+  <si>
+    <t>[单位21]复印纸</t>
+  </si>
+  <si>
     <t>老干部支部打印费用</t>
   </si>
   <si>
     <t>电子配件等报销</t>
   </si>
   <si>
-    <t>宜城[地点]所报快艇加油费（[城市]市[地点]加油点）</t>
-  </si>
-  <si>
-    <t>督察领维权抚慰激励金（[姓名1]）</t>
-  </si>
-  <si>
-    <t>情指中心报新警初任培训[数字]人（[姓名2]）</t>
-  </si>
-  <si>
-    <t>[日期]-[数字]巡特警车辆维修费（[城市]经济技术开发区[单位1]）</t>
-  </si>
-  <si>
-    <t>[年份]年[月份]月社保单位部分</t>
-  </si>
-  <si>
-    <t>[地点]楼会议室光缆布放（[单位2]）</t>
-  </si>
-  <si>
-    <t>[地点]水上所买健身器材一批[数字]-[数字]（[单位3]）</t>
-  </si>
-  <si>
-    <t>[日期]-[日期]保安服务费（[单位4]）</t>
-  </si>
-  <si>
-    <t>市局空调维修费（[单位5]）</t>
-  </si>
-  <si>
-    <t>退休人员报学费（[姓名3]）</t>
-  </si>
-  <si>
-    <t>市局电脑设备维修配件（[单位6]）</t>
-  </si>
-  <si>
-    <t>通信保障买[品牌]高清会议系统一套[数字]-[数字]（[单位7]）</t>
-  </si>
-  <si>
-    <t>[地点]警务站报[年份]年新警入警培训（[姓名4]）</t>
-  </si>
-  <si>
-    <t>[地点]警务站报基层政工干部培训（[姓名5]）</t>
-  </si>
-  <si>
-    <t>[地点]警务站报模拟警情处置培训（[姓名6]）</t>
-  </si>
-  <si>
-    <t>[地点]水上所报厨房线路安装、管道疏通费（[姓名7]）</t>
-  </si>
-  <si>
-    <t>市局[月份]月各部门车维修费（[单位8]）</t>
-  </si>
-  <si>
-    <t>[城市]政工干部培训班费用（[姓名8]）</t>
-  </si>
-  <si>
-    <t>[年份]年[月份]月社保个人部分</t>
-  </si>
-  <si>
-    <t>[单位9]中队报垃圾清运费（[姓名9]）</t>
-  </si>
-  <si>
-    <t>退休支部报印刷品（[单位10]）</t>
-  </si>
-  <si>
-    <t>[月份]月公办公积金个人</t>
-  </si>
-  <si>
-    <t>[月份]月养老金</t>
-  </si>
-  <si>
-    <t>人口报基础所长班培训费（[姓名10]）</t>
-  </si>
-  <si>
-    <t>（[单位11]）[月份]月外聘人员工资</t>
-  </si>
-  <si>
-    <t>单位教职工[数字]月份工资</t>
-  </si>
-  <si>
-    <t>（[单位12]）外聘人员社会保障代扣专户拨款</t>
-  </si>
-  <si>
-    <t>[月份]月公办养老金单位</t>
-  </si>
-  <si>
-    <t>[单位13]在编人员公积金单位</t>
-  </si>
-  <si>
-    <t>支付非编教职工[数字]月社保</t>
-  </si>
-  <si>
-    <t>人口报基础所长班培训费（[姓名11]）</t>
-  </si>
-  <si>
-    <t>[姓名12]报会议服务</t>
-  </si>
-  <si>
-    <t>[单位14]培训费</t>
-  </si>
-  <si>
-    <t>下水管道疏通及维修费（[单位15]）</t>
-  </si>
-  <si>
-    <t>[月份]月物业服务费</t>
-  </si>
-  <si>
-    <t>[单位16]垃圾处理费</t>
-  </si>
-  <si>
-    <t>[姓名13]报公务接待</t>
-  </si>
-  <si>
-    <t>[姓名14]报洗车费</t>
-  </si>
-  <si>
-    <t>[年份]年第[数字]季度保安费</t>
-  </si>
-  <si>
-    <t>[姓名15]报租车费</t>
-  </si>
-  <si>
-    <t>[数字]季度公车运维</t>
-  </si>
-  <si>
-    <t>[姓名16]报洗车费</t>
-  </si>
-  <si>
-    <t>[月份]月公车运维</t>
-  </si>
-  <si>
-    <t>[日期]-[日期]月公车运维</t>
-  </si>
-  <si>
-    <t>[单位17]文印费</t>
-  </si>
-  <si>
-    <t>办公室：[地点]调研公务接待费用（[单位18]）</t>
-  </si>
-  <si>
-    <t>（[单位19]）文印室耗材费</t>
-  </si>
-  <si>
-    <t>禁毒买印刷品（[单位20]）</t>
-  </si>
-  <si>
-    <t>[数字]购铲刀、链条</t>
-  </si>
-  <si>
-    <t>[单位21]复印纸</t>
-  </si>
-  <si>
     <t>[日期]日接待[上级单位]局长[姓名17]异性来宜调研共[数字]人</t>
   </si>
   <si>
@@ -250,6 +257,9 @@
     <t>接待[城市]大走访</t>
   </si>
   <si>
+    <t>接待[城市]局来基层联系</t>
+  </si>
+  <si>
     <t>接待[城市]统计局法制监督检查</t>
   </si>
   <si>
@@ -257,22 +267,23 @@
   </si>
   <si>
     <t>接待[地点][单位23]</t>
-  </si>
-  <si>
-    <t>接待[城市]局来基层联系</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -280,7 +291,29 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -288,16 +321,22 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="等线 Light"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -306,7 +345,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -315,31 +353,6 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -347,7 +360,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -356,7 +368,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -365,15 +376,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -382,24 +384,13 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -408,7 +399,27 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -416,14 +427,6 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -437,175 +440,188 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -615,6 +631,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -640,7 +671,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
@@ -675,15 +706,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -699,17 +721,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -725,131 +741,152 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -858,58 +895,61 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="标题" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="标题 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="标题 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="标题 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="检查单元格" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="解释性文本" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="警告文本" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="链接单元格" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="适中" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="输出" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="着色 1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="着色 2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="着色 3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="着色 4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="着色 5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -958,7 +998,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -991,26 +1031,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1043,23 +1066,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1221,24 +1227,19 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3196EC4-462F-43C8-A622-3CD078BE4037}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C71"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="57.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1249,7 +1250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1260,678 +1261,678 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C28" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C31" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C32" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C34" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C35" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36">
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C36" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37">
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38">
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C38" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39">
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="C39" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40">
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41">
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C41" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42">
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C42" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43">
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C43" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44">
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="C44" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45">
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46">
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="C46" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47">
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C47" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48">
         <v>46</v>
       </c>
       <c r="B48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" t="s">
         <v>16</v>
       </c>
-      <c r="C48" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49">
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="C49" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50">
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C50" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51">
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C51" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52">
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C52" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53">
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54">
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C54" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55">
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C55" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
       <c r="A56">
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C56" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57">
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C57" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
       <c r="A58">
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C58" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
       <c r="A59">
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="C59" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
       <c r="A60">
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C60" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
       <c r="A61">
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C61" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62">
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="C62" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
       <c r="A63">
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="C63" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
       <c r="A64">
         <v>62</v>
       </c>
@@ -1939,10 +1940,10 @@
         <v>72</v>
       </c>
       <c r="C64" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
       <c r="A65">
         <v>63</v>
       </c>
@@ -1950,10 +1951,10 @@
         <v>73</v>
       </c>
       <c r="C65" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66">
         <v>64</v>
       </c>
@@ -1961,10 +1962,10 @@
         <v>74</v>
       </c>
       <c r="C66" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
       <c r="A67">
         <v>65</v>
       </c>
@@ -1972,58 +1973,58 @@
         <v>75</v>
       </c>
       <c r="C67" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
       <c r="A68">
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C68" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
       <c r="A69">
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C69" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
       <c r="A70">
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C70" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71">
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C71" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C71">
+  <sortState ref="A2:C71">
     <sortCondition ref="A43:A71"/>
   </sortState>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>